--- a/renommage-mapping/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/renommage-mapping/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T12:29:29+00:00</t>
+    <t>2025-10-21T13:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -180,7 +180,7 @@
     <t>FRLMPersonneStructure.structure</t>
   </si>
   <si>
-    <t>FRLMPersonneStructure.representedOrganization</t>
+    <t>assignedEntity.representedOrganization</t>
   </si>
   <si>
     <t>FRLMPersonneStructure.structure.identifiantStructure</t>
@@ -247,9 +247,6 @@
   </si>
   <si>
     <t>PractitionerRole.Practitioner.name.suffix</t>
-  </si>
-  <si>
-    <t>assignedEntity.representedOrganization</t>
   </si>
   <si>
     <t>PractitionerRole.Organization</t>
@@ -944,14 +941,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -964,7 +961,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -977,7 +974,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -990,7 +987,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -1003,7 +1000,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -1016,7 +1013,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
     </row>

--- a/renommage-mapping/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/renommage-mapping/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T13:02:53+00:00</t>
+    <t>2025-10-21T13:05:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/renommage-mapping/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/renommage-mapping/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T13:05:45+00:00</t>
+    <t>2025-10-21T13:27:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/renommage-mapping/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
+++ b/renommage-mapping/ig/mappingPersonneStructureAssignedEntityFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T13:27:14+00:00</t>
+    <t>2025-10-21T14:51:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
